--- a/results/att_summary_survey.xlsx
+++ b/results/att_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4119396667161183</v>
+        <v>0.4119231277135925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03659672575618315</v>
+        <v>0.03551662021466755</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3402114022819099</v>
+        <v>0.3423118312402568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4836679311503267</v>
+        <v>0.4815344241869281</v>
       </c>
       <c r="G2" t="n">
-        <v>2.158943053597389e-29</v>
+        <v>4.216315028049169e-31</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5002094490957281</v>
+        <v>0.499321025741696</v>
       </c>
       <c r="I2" t="n">
-        <v>12.40329825638439</v>
+        <v>12.3811198157209</v>
       </c>
       <c r="J2" t="n">
         <v>3.79917864476386</v>
       </c>
       <c r="K2" t="n">
-        <v>3.37995299399328</v>
+        <v>3.380620028518702</v>
       </c>
       <c r="L2" t="n">
         <v>7220</v>
       </c>
       <c r="M2" t="n">
-        <v>554.8407173044708</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="N2" t="n">
-        <v>6.476829160792168e-29</v>
+        <v>1.264894508414751e-30</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.04660944779469506</v>
+        <v>-0.04579550992862554</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,37 +591,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0397320753594812</v>
+        <v>0.0390974269238365</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1244828845303095</v>
+        <v>-0.1224250585875317</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03126398894091942</v>
+        <v>0.03083403873028063</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2407582275589254</v>
+        <v>0.2414710814149404</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.04399205111521829</v>
+        <v>-0.04256676218162255</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.297296446854563</v>
+        <v>-1.255616935124939</v>
       </c>
       <c r="J3" t="n">
         <v>3.137782340862423</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1790237023983</v>
+        <v>3.177681852344857</v>
       </c>
       <c r="L3" t="n">
         <v>7220</v>
       </c>
       <c r="M3" t="n">
-        <v>554.8407173044708</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2407582275589254</v>
+        <v>0.2414710814149404</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2591768318423447</v>
+        <v>0.2582177129441012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,37 +648,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03580784780244857</v>
+        <v>0.03790343166340342</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1889947397856538</v>
+        <v>0.1839283519933554</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3293589238990356</v>
+        <v>0.332507073894847</v>
       </c>
       <c r="G4" t="n">
-        <v>4.553841777150192e-13</v>
+        <v>9.590676754514887e-12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2953172367768869</v>
+        <v>0.295112936491181</v>
       </c>
       <c r="I4" t="n">
-        <v>9.996169724695719</v>
+        <v>9.981897038554871</v>
       </c>
       <c r="J4" t="n">
         <v>3.061396303901438</v>
       </c>
       <c r="K4" t="n">
-        <v>2.783184461389577</v>
+        <v>2.783545643723753</v>
       </c>
       <c r="L4" t="n">
         <v>7220</v>
       </c>
       <c r="M4" t="n">
-        <v>554.8407173044708</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="N4" t="n">
-        <v>6.830762665725288e-13</v>
+        <v>1.438601513177233e-11</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
